--- a/docs/sample-output/07-self-storage/estimate.xlsx
+++ b/docs/sample-output/07-self-storage/estimate.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="348">
   <si>
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Bayside Climate Storage · Total $17,790,423</t>
+    <t>Total Project Cost — Summary   ·   Bayside Climate Storage · Total $17,701,929</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   Bayside Climate Storage · Total $17,790,423</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   Bayside Climate Storage · Total $17,701,929</t>
   </si>
   <si>
     <t>Component</t>
@@ -147,7 +147,7 @@
     <t>within ($85–$280)</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Bayside Climate Storage · Total $17,790,423</t>
+    <t>Cost by Phase   ·   Bayside Climate Storage · Total $17,701,929</t>
   </si>
   <si>
     <t>Phase</t>
@@ -189,7 +189,7 @@
     <t>5.2%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Bayside Climate Storage · Total $17,790,423</t>
+    <t>Line-Item Detail   ·   Bayside Climate Storage · Total $17,701,929</t>
   </si>
   <si>
     <t>Group</t>
@@ -453,7 +453,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Bayside Climate Storage · Total $17,790,423</t>
+    <t>Draw Schedules   ·   Bayside Climate Storage · Total $17,701,929</t>
   </si>
   <si>
     <t>PHASE 1 — MONTHLY DRAWS</t>
@@ -510,7 +510,7 @@
     <t>2028-05</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Bayside Climate Storage · Total $17,790,423</t>
+    <t>Sources &amp; Assumptions   ·   Bayside Climate Storage · Total $17,701,929</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -546,7 +546,7 @@
     <t>LTC 60%, rate 7.00%, fee 1.00%</t>
   </si>
   <si>
-    <t>SOURCES (45)</t>
+    <t>SOURCES (46)</t>
   </si>
   <si>
     <t>Ref</t>
@@ -1045,6 +1045,21 @@
   </si>
   <si>
     <t>204.37 USD/sf (2026)</t>
+  </si>
+  <si>
+    <t>residential/single-family.json#e10</t>
+  </si>
+  <si>
+    <t>Cost of Constructing a Home-2024 (Special Study for Housing Economics)</t>
+  </si>
+  <si>
+    <t>National Association of Home Builders (Eric Lynch)</t>
+  </si>
+  <si>
+    <t>26747 USD/unit (2024)</t>
+  </si>
+  <si>
+    <t>https://nahb.org/-/media/AB4EFC742624475A97A0A62189986FF8.ashx</t>
   </si>
 </sst>
 </file>
@@ -1642,7 +1657,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>770533.42</v>
+        <v>693984</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1650,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>571982.91</v>
+        <v>568706.59</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1658,7 +1673,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>436867.84</v>
+        <v>433557.06</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1666,7 +1681,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>198153.21</v>
+        <v>192794.75</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1674,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>4068564.13</v>
+        <v>3980069.15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1690,7 +1705,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1729,7 +1744,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>7682228.325227272</v>
+        <v>7644014.5838636365</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1857,19 +1872,19 @@
         <v>11239859.36</v>
       </c>
       <c r="E5" s="13">
-        <v>4068564.13</v>
+        <v>3980069.15</v>
       </c>
       <c r="F5" s="13">
         <v>2482000</v>
       </c>
       <c r="G5" s="13">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
       <c r="H5" s="13">
-        <v>202.16390329545453</v>
+        <v>201.1582785227273</v>
       </c>
       <c r="I5" s="14">
-        <v>152.00293480861242</v>
+        <v>151.2468259569378</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>42</v>
@@ -1885,13 +1900,13 @@
         <v>11239859.36</v>
       </c>
       <c r="E6" s="16">
-        <v>4068564.13</v>
+        <v>3980069.15</v>
       </c>
       <c r="F6" s="16">
         <v>2482000</v>
       </c>
       <c r="G6" s="16">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -2007,19 +2022,19 @@
         <v>11239859.36</v>
       </c>
       <c r="G5" s="13">
-        <v>4068564.13</v>
+        <v>3980069.15</v>
       </c>
       <c r="H5" s="13">
         <v>2482000</v>
       </c>
       <c r="I5" s="13">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
       <c r="J5" s="13">
-        <v>10674254.09</v>
+        <v>10621157.11</v>
       </c>
       <c r="K5" s="13">
-        <v>330125.3</v>
+        <v>327345.49</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2034,13 +2049,13 @@
         <v>11239859.36</v>
       </c>
       <c r="G6" s="16">
-        <v>4068564.13</v>
+        <v>3980069.15</v>
       </c>
       <c r="H6" s="16">
         <v>2482000</v>
       </c>
       <c r="I6" s="16">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -3121,10 +3136,10 @@
         <v>129</v>
       </c>
       <c r="H38" s="14">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I38" s="13">
-        <v>141565.15</v>
+        <v>99695.26</v>
       </c>
       <c r="J38" s="12" t="s">
         <v>69</v>
@@ -3153,10 +3168,10 @@
         <v>129</v>
       </c>
       <c r="H39" s="14">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I39" s="13">
-        <v>134374.79</v>
+        <v>99695.26</v>
       </c>
       <c r="J39" s="12" t="s">
         <v>69</v>
@@ -3186,7 +3201,7 @@
       </c>
       <c r="H40" s="18"/>
       <c r="I40" s="13">
-        <v>198153.21</v>
+        <v>192794.75</v>
       </c>
       <c r="J40" s="12" t="s">
         <v>69</v>
@@ -3332,7 +3347,7 @@
       </c>
       <c r="H45" s="18"/>
       <c r="I45" s="13">
-        <v>571982.91</v>
+        <v>568706.59</v>
       </c>
       <c r="J45" s="12" t="s">
         <v>69</v>
@@ -3360,7 +3375,7 @@
       </c>
       <c r="H46" s="18"/>
       <c r="I46" s="13">
-        <v>330125.3</v>
+        <v>327345.49</v>
       </c>
       <c r="J46" s="12" t="s">
         <v>69</v>
@@ -3388,7 +3403,7 @@
       </c>
       <c r="H47" s="18"/>
       <c r="I47" s="13">
-        <v>106742.54</v>
+        <v>106211.57</v>
       </c>
       <c r="J47" s="12" t="s">
         <v>69</v>
@@ -3408,7 +3423,7 @@
       <c r="G48" s="15"/>
       <c r="H48" s="15"/>
       <c r="I48" s="16">
-        <v>17790423.49</v>
+        <v>17701928.51</v>
       </c>
       <c r="J48" s="15"/>
     </row>
@@ -3507,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>1978650.48</v>
+        <v>1902101.06</v>
       </c>
       <c r="D6" s="13">
         <v>2482000</v>
       </c>
       <c r="E6" s="13">
-        <v>4567393.02</v>
+        <v>4490312.63</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -3533,13 +3548,13 @@
         <v>140903.38</v>
       </c>
       <c r="C7" s="13">
-        <v>118074.71</v>
+        <v>117457.95</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>258978.09</v>
+        <v>258361.33</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -3559,13 +3574,13 @@
         <v>415644.6</v>
       </c>
       <c r="C8" s="13">
-        <v>118074.71</v>
+        <v>117457.94</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>533719.31</v>
+        <v>533102.54</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -3585,13 +3600,13 @@
         <v>669543.7</v>
       </c>
       <c r="C9" s="13">
-        <v>118074.71</v>
+        <v>117457.94</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>787618.41</v>
+        <v>787001.64</v>
       </c>
       <c r="F9" s="13">
         <v>0</v>
@@ -3611,22 +3626,22 @@
         <v>889869.14</v>
       </c>
       <c r="C10" s="13">
-        <v>118074.7</v>
+        <v>117457.93</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="13">
-        <v>968460.57</v>
+        <v>1007327.07</v>
       </c>
       <c r="F10" s="13">
-        <v>39483.27</v>
+        <v>0</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
       </c>
       <c r="H10" s="13">
-        <v>39483.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3637,22 +3652,22 @@
         <v>1065572.75</v>
       </c>
       <c r="C11" s="13">
-        <v>118074.72</v>
+        <v>117457.95</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="13">
+        <v>4666.19</v>
+      </c>
+      <c r="F11" s="13">
+        <v>1178364.51</v>
+      </c>
+      <c r="G11" s="13">
         <v>0</v>
       </c>
-      <c r="F11" s="13">
-        <v>1183647.47</v>
-      </c>
-      <c r="G11" s="13">
-        <v>230.32</v>
-      </c>
       <c r="H11" s="13">
-        <v>1223361.06</v>
+        <v>1178364.51</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3663,7 +3678,7 @@
         <v>1187844.11</v>
       </c>
       <c r="C12" s="13">
-        <v>118074.7</v>
+        <v>117457.93</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
@@ -3672,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>1305918.81</v>
+        <v>1305302.04</v>
       </c>
       <c r="G12" s="13">
-        <v>7136.27</v>
+        <v>6873.79</v>
       </c>
       <c r="H12" s="13">
-        <v>2536416.14</v>
+        <v>2490540.34</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3689,7 +3704,7 @@
         <v>1250551.98</v>
       </c>
       <c r="C13" s="13">
-        <v>118074.71</v>
+        <v>117457.95</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
@@ -3698,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>1368626.69</v>
+        <v>1368009.93</v>
       </c>
       <c r="G13" s="13">
-        <v>14795.76</v>
+        <v>14528.15</v>
       </c>
       <c r="H13" s="13">
-        <v>3919838.59</v>
+        <v>3873078.42</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3715,7 +3730,7 @@
         <v>1250552.03</v>
       </c>
       <c r="C14" s="13">
-        <v>118074.69</v>
+        <v>117457.92</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
@@ -3724,13 +3739,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>1368626.72</v>
+        <v>1368009.95</v>
       </c>
       <c r="G14" s="13">
-        <v>22865.73</v>
+        <v>22592.96</v>
       </c>
       <c r="H14" s="13">
-        <v>5311331.04</v>
+        <v>5263681.33</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3741,7 +3756,7 @@
         <v>1187844.1</v>
       </c>
       <c r="C15" s="13">
-        <v>118074.74</v>
+        <v>117457.96</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
@@ -3750,13 +3765,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>1305918.84</v>
+        <v>1305302.06</v>
       </c>
       <c r="G15" s="13">
-        <v>30982.76</v>
+        <v>30704.81</v>
       </c>
       <c r="H15" s="13">
-        <v>6648232.64</v>
+        <v>6599688.2</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3767,7 +3782,7 @@
         <v>1065572.73</v>
       </c>
       <c r="C16" s="13">
-        <v>118074.68</v>
+        <v>117457.91</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
@@ -3776,13 +3791,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>1183647.41</v>
+        <v>1183030.64</v>
       </c>
       <c r="G16" s="13">
-        <v>38781.36</v>
+        <v>38498.18</v>
       </c>
       <c r="H16" s="13">
-        <v>7870661.41</v>
+        <v>7821217.02</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3793,7 +3808,7 @@
         <v>889869.14</v>
       </c>
       <c r="C17" s="13">
-        <v>118074.68</v>
+        <v>117457.91</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
@@ -3802,13 +3817,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>1007943.82</v>
+        <v>1007327.05</v>
       </c>
       <c r="G17" s="13">
-        <v>45912.19</v>
+        <v>45623.77</v>
       </c>
       <c r="H17" s="13">
-        <v>8924517.42</v>
+        <v>8874167.84</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3819,7 +3834,7 @@
         <v>669543.7</v>
       </c>
       <c r="C18" s="13">
-        <v>118074.68</v>
+        <v>117457.91</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
@@ -3828,13 +3843,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>787618.38</v>
+        <v>787001.61</v>
       </c>
       <c r="G18" s="13">
-        <v>52059.68</v>
+        <v>51765.98</v>
       </c>
       <c r="H18" s="13">
-        <v>9764195.48</v>
+        <v>9712935.43</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3845,7 +3860,7 @@
         <v>415644.6</v>
       </c>
       <c r="C19" s="13">
-        <v>118074.72</v>
+        <v>117457.95</v>
       </c>
       <c r="D19" s="13">
         <v>0</v>
@@ -3854,13 +3869,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>533719.32</v>
+        <v>533102.55</v>
       </c>
       <c r="G19" s="13">
-        <v>56957.81</v>
+        <v>56658.79</v>
       </c>
       <c r="H19" s="13">
-        <v>10354872.61</v>
+        <v>10302696.77</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3871,7 +3886,7 @@
         <v>140903.4</v>
       </c>
       <c r="C20" s="13">
-        <v>118074.66</v>
+        <v>117457.88</v>
       </c>
       <c r="D20" s="13">
         <v>0</v>
@@ -3880,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>258978.06</v>
+        <v>258361.28</v>
       </c>
       <c r="G20" s="13">
-        <v>60403.42</v>
+        <v>60099.06</v>
       </c>
       <c r="H20" s="13">
-        <v>10674254.09</v>
+        <v>10621157.11</v>
       </c>
     </row>
   </sheetData>
@@ -3908,7 +3923,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4913,6 +4928,26 @@
       </c>
       <c r="F56" s="12" t="s">
         <v>332</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
